--- a/etf_holdings/2026-10-25_00993A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-25_00993A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-25 21:24:07</t>
+          <t>2026-10-25 21:45:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-25 21:24:07</t>
+          <t>2026-10-25 21:45:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25 21:24:07</t>
+          <t>2026-10-25 21:45:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25 21:24:07</t>
+          <t>2026-10-25 21:45:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-25 21:24:07</t>
+          <t>2026-10-25 21:45:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-25 21:24:07</t>
+          <t>2026-10-25 21:45:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-25 21:24:07</t>
+          <t>2026-10-25 21:45:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-25 21:24:07</t>
+          <t>2026-10-25 21:45:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-25 21:24:07</t>
+          <t>2026-10-25 21:45:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-25 21:24:07</t>
+          <t>2026-10-25 21:45:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-25 21:24:07</t>
+          <t>2026-10-25 21:45:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-25 21:24:07</t>
+          <t>2026-10-25 21:45:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-25 21:24:07</t>
+          <t>2026-10-25 21:45:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-25 21:24:07</t>
+          <t>2026-10-25 21:45:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-25 21:24:07</t>
+          <t>2026-10-25 21:45:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1393,6 +1393,1836 @@
         </is>
       </c>
       <c r="M16" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:04</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>4958臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-1.9%567</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-1.9%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>567</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1.97%328,000</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1.97%</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>328000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:04</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1560中砂</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-3.53%846</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-3.53%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>846</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.91%210,000</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>210000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.07%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:04</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3711日月光投控</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-4.39%654</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-4.39%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>654</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1.83%258,000</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1.83%</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>258000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:04</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2408南亞科</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-5.15%414</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-5.15%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>414</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1.65%363,000</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.65%</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>363000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:04</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3653健策</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-7.12%6070</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-7.12%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>6070</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1.56%23,000</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.56%</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>23000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:04</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2347聯強</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-0.4%99.3</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1.51%1,456,000</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1.51%</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1456000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:04</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2327國巨*</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-6.46%507</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-6.46%</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>507</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1.41%251,000</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1.41%</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>251000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:04</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>3406玉晶光</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>+1.75%1160</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>+1.75%</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1160</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1.37%116,000</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>116000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>+0.02%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:04</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2368金像電</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-6.69%1115</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-6.69%</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1115</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1.25%101,000</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1.25%</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>101000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:04</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2455全新</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-4.79%467</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-4.79%</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>467</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1.23%242,000</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1.23%</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>242000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:04</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>6805富世達</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-2.51%2335</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-2.51%</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>2335</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1.19%48,000</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1.19%</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>48000</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:04</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3105穩懋</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-5.08%486</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-5.08%</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>486</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1.14%214,000</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1.14%</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>214000</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-0.06%</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:04</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>6669緯穎</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-2.13%1840</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-2.13%</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>1840</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1.08%55,191</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>1.08%</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>55191</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:04</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>6196帆宣</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-2.93%597</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-2.93%</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>597</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0.93%145,000</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.93%</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>145000</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-0.03%</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:04</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2395研華</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-1.9%670</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-1.9%</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>670</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.92%130,000</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.92%</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>130000</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:05</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2308台達電</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-4%1560</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-4%</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1560</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.88%52,000</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.88%</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>52000</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:05</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3008大立光</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>+0.08%6175</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>+0.08%</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>6175</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0.83%13,000</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.83%</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:05</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>8996高力</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-6.02%1560</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-6.02%</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>1560</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0.76%44,000</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.76%</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>44000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:05</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2345智邦</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-2.2%1775</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-2.2%</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>1775</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0.62%33,000</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>33000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:05</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3665貿聯-KY</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-3.85%1875</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-3.85%</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>1875</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0.61%30,000</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:05</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2313華通</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-6.65%224.5</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-6.65%</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>224.5</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.60%241,000</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.60%</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>241000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-0.04%</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:05</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>6505台塑化</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-2.74%106.5</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-2.74%</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.54%478,000</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>478000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:05</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2360致茂</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-1.49%1980</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-1.49%</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>1980</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.52%25,000</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.52%</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:05</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2603長榮</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>+0.97%260</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>+0.97%</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>260</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.50%186,000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>186000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:05</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2027大成鋼</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>+1.4%50.6</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>+1.4%</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0.44%856,000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.44%</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>856000</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:05</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>6147頎邦</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-4.92%203</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-4.92%</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>203</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.39%174,000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>174000</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:05</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3044健鼎</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-4.63%556</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-4.63%</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>556</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0.38%62,000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>62000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:05</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2006東和鋼鐵</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-0.11%93.2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-0.11%</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0.37%379,000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>379000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:05</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3491昇達科</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-7.69%1320</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-7.69%</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>1320</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0.30%20,000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-25 21:45:05</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2344華邦電</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-3.13%154.5</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-3.13%</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.27%165,000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>165000</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-0.01%</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>
